--- a/summer_camps/018_packing_list_form--summer_camps.xlsx
+++ b/summer_camps/018_packing_list_form--summer_camps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>packing_list_form_page_1</t>
+          <t>general_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Packing List</t>
+          <t>General Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>packing_list_form_page_2</t>
+          <t>packing_clothing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Important Items</t>
+          <t>What type of clothing do you want to pack?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>packing_list_form_page_2</t>
+          <t>medications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Extra Items</t>
+          <t>Do you have any medications that you need to pack?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,43 +584,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>packing_list_form_page_3</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Important Items</t>
+          <t>List any special equipment you need to bring?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>packing_list_form_page_3</t>
+          <t>camp_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Extra Items</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is your camp date?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,22 +634,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>packing_list_form_page_5</t>
+          <t>arrival_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>What time do you need to arrive at camp?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Date should be in MM/DD/YYYY format</t>
+          <t>HH -MM AM/PM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -657,24 +661,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>packing_list_form_page_5</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Time should be 4 digits</t>
-        </is>
-      </c>
+          <t>What is your phone number?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -689,12 +689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>packing_list_form_page_6</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>What is your email?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -712,12 +712,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>packing_list_form_page_7</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Do you have any medical conditions that we need to know about?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -730,17 +730,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>packing_list_form_page_7</t>
+          <t>dietary_requirements</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Do you have any dietary requirements?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -758,12 +758,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>packing_list_form_page_8</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>packing_list_form__page_8</t>
+          <t>Is there anything else you want to tell us about yourself?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -781,12 +781,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>packing_list_form_page_8</t>
+          <t>questions_concerns</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>packing_list_form__page_8</t>
+          <t>Do you have any questions or concerns about camp?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,17 +799,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>packing_list_form_page_9</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>packing_list_form__page_9</t>
+          <t>Do you need any help with transportation?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -827,12 +827,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>packing_list_form_page_9</t>
+          <t>more_info</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>packing_list_form__page_9</t>
+          <t>Do you have any other information you want to share?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -850,12 +850,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>packing_list_form_page_10</t>
+          <t>child_info</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>packing_list_form__page_10</t>
+          <t>Is there anything else you want to say about your child?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -873,12 +873,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>packing_list_form_page_11</t>
+          <t>first_time_camper</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>packing_list_form__page_11</t>
+          <t>Are you a first-time camper?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -896,12 +896,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>packing_list_form_page_12</t>
+          <t>buddy_program</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>packing_list_form__page_12</t>
+          <t>Do you want to join a buddy program?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -919,12 +919,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>packing_list_form_page_13</t>
+          <t>behavioral_comments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>packing_list_form__page_13</t>
+          <t>Do you have any comments or concerns about your child's behavior?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -942,12 +942,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>packing_list_form_page_14</t>
+          <t>additional_forms</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>packing_list_form__page_14</t>
+          <t>Do you need any additional forms or documentation?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -965,131 +965,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>packing_list_form_page_15</t>
+          <t>final_comments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>packing_list_form__page_15</t>
+          <t>Is there anything else you want to tell us?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>packing_list_form_page_16</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>packing_list_form__page_16</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>packing_list_form_page_17</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>packing_list_form__page_17</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>packing_list_form_page_18</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>packing_list_form__page_18</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>packing_list_form_page_19</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>packing_list_form__page_19</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>packing_list_form_page_20</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>packing_list_form__page_20</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1109,9 +994,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1134,102 +1019,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>packing_list_form_page_3_choices</t>
+          <t>medications_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>packing_list_form_page_3_choices</t>
+          <t>medications_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>packing_list_form_page_3_choices</t>
+          <t>dietary_requirements_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>packing_list_form_page_3_choices</t>
+          <t>dietary_requirements_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Item 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>packing_list_form_page_3_choices</t>
+          <t>transportation_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Item 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>packing_list_form_page_3_choices</t>
+          <t>transportation_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Item 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
